--- a/uploads/monday schedule.xlsx
+++ b/uploads/monday schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\GitHub\nso_schedules\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC1EB48A-291D-4085-A5A7-6B6E26986820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1D5F49C-0F41-4779-90F1-856540D9CCD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="209">
   <si>
     <t>Delanie Owens</t>
   </si>
@@ -621,9 +621,6 @@
   <si>
     <t xml:space="preserve">Legacy Walk Clean-up
 2:00 PM - end </t>
-  </si>
-  <si>
-    <t>black</t>
   </si>
   <si>
     <t>Arrive at the Biddulph. Drop stuff off at the Spori and Amphitheater.</t>
@@ -2012,73 +2009,73 @@
       <c r="A167" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B167" t="s">
+      <c r="B167">
+        <v>1</v>
+      </c>
+      <c r="C167" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="C167" s="5" t="s">
+      <c r="D167" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="D167" s="5" t="s">
+      <c r="E167" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="E167" s="5" t="s">
+      <c r="F167" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="F167" s="5" t="s">
+      <c r="G167" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="G167" s="5" t="s">
+      <c r="H167" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="H167" s="5" t="s">
+      <c r="I167" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="I167" s="5" t="s">
+      <c r="J167" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="J167" s="5" t="s">
+      <c r="K167" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="K167" s="5" t="s">
+      <c r="L167" s="5" t="s">
         <v>201</v>
-      </c>
-      <c r="L167" s="5" t="s">
-        <v>202</v>
       </c>
       <c r="M167" s="5"/>
       <c r="N167" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="O167" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="P167" s="5"/>
       <c r="Q167" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="R167" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="S167" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="R167" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="S167" s="5" t="s">
+      <c r="T167" s="5" t="s">
         <v>205</v>
-      </c>
-      <c r="T167" s="5" t="s">
-        <v>206</v>
       </c>
       <c r="U167" s="5"/>
       <c r="V167" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="W167" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="X167" s="5"/>
       <c r="Y167" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Z167" s="5"/>
       <c r="AA167" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>
